--- a/M&A/カンテサンス/カンテサンス_CF計画_三つ星維持_2027-2032.xlsx
+++ b/M&A/カンテサンス/カンテサンス_CF計画_三つ星維持_2027-2032.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="133">
   <si>
     <r>
       <rPr>
@@ -842,6 +842,118 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">【子会社】カンテサンスプラスの現預金（役員借入金返済後 約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.37</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億円）を決済時の手元資金に加算。ブリッジ返済原資</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">21.4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億円（プティ・ボノム単体の現預金</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">17.4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＋役員貸付金</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5.0−</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">留保</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）には含めていないため、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SPC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の必要資金を減らす方に使うこともできる。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">【モデルの簡略化】運転資本の増減は無視。法人税は発生年度に納付（</t>
     </r>
     <r>
@@ -2540,6 +2652,268 @@
     <r>
       <rPr>
         <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">■ 子会社 カンテサンスプラス株式会社（プティ・ボノム</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100%</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">子会社）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">子会社の現預金</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6E6368"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6E6368"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6E6368"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">期（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6E6368"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6E6368"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6E6368"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6E6368"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月期）決算書：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6E6368"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">42,906,344</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6E6368"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">子会社の役員借入金（岸田様への返済）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6E6368"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6E6368"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6E6368"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">期（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6E6368"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6E6368"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6E6368"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6E6368"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月期）決算書：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6E6368"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5,543,167</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6E6368"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円。決済までに返済する前提で控除</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">決済時に使える子会社の現預金</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6E6368"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配当（完全子法人からの配当は益金不算入・源泉徴収なし）又は合併で親会社に移す。年間の利益（約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6E6368"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6E6368"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円）は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6E6368"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF6E6368"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に含めず保守的に試算</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="14"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
@@ -2995,6 +3369,9 @@
       </rPr>
       <t xml:space="preserve">CF</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">期末現金残高（子会社の現預金を含む）</t>
   </si>
   <si>
     <r>
@@ -3569,7 +3946,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3671,6 +4048,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3978,8 +4363,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H40"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="0" width="11"/>
@@ -4197,27 +4582,27 @@
       </c>
       <c r="B11" s="7" t="n">
         <f aca="false">CF_借入15億!C31</f>
-        <v>183.031181940744</v>
+        <v>220.431181940744</v>
       </c>
       <c r="C11" s="7" t="n">
         <f aca="false">CF_借入15億!D31</f>
-        <v>303.329141488992</v>
+        <v>340.729141488992</v>
       </c>
       <c r="D11" s="7" t="n">
         <f aca="false">CF_借入15億!E31</f>
-        <v>435.341349749045</v>
+        <v>472.741349749045</v>
       </c>
       <c r="E11" s="7" t="n">
         <f aca="false">CF_借入15億!F31</f>
-        <v>331.868825861446</v>
+        <v>369.268825861446</v>
       </c>
       <c r="F11" s="7" t="n">
         <f aca="false">CF_借入15億!G31</f>
-        <v>242.782794657677</v>
+        <v>280.182794657677</v>
       </c>
       <c r="G11" s="7" t="n">
         <f aca="false">CF_借入15億!H31</f>
-        <v>431.09979998753</v>
+        <v>468.49979998753</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4293,7 +4678,7 @@
       </c>
       <c r="B15" s="8" t="n">
         <f aca="false">MIN(B11:G11)</f>
-        <v>183.031181940744</v>
+        <v>220.431181940744</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4507,27 +4892,27 @@
       </c>
       <c r="B25" s="7" t="n">
         <f aca="false">CF_借入20億!C31</f>
-        <v>106.606375920992</v>
+        <v>144.006375920992</v>
       </c>
       <c r="C25" s="7" t="n">
         <f aca="false">CF_借入20億!D31</f>
-        <v>149.608455318656</v>
+        <v>187.008455318656</v>
       </c>
       <c r="D25" s="7" t="n">
         <f aca="false">CF_借入20億!E31</f>
-        <v>203.41886633206</v>
+        <v>240.81886633206</v>
       </c>
       <c r="E25" s="7" t="n">
         <f aca="false">CF_借入20億!F31</f>
-        <v>20.8023914179043</v>
+        <v>58.2023914179043</v>
       </c>
       <c r="F25" s="7" t="n">
         <f aca="false">CF_借入20億!G31</f>
-        <v>-148.407430743525</v>
+        <v>-111.007430743525</v>
       </c>
       <c r="G25" s="7" t="n">
         <f aca="false">CF_借入20億!H31</f>
-        <v>-41.2332498996806</v>
+        <v>-3.83324989968057</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4603,7 +4988,7 @@
       </c>
       <c r="B29" s="8" t="n">
         <f aca="false">MIN(B25:G25)</f>
-        <v>-148.407430743525</v>
+        <v>-111.007430743525</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4612,7 +4997,7 @@
       </c>
       <c r="B30" s="13" t="n">
         <f aca="false">MAX(0,-B29)</f>
-        <v>148.407430743525</v>
+        <v>111.007430743525</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4690,12 +5075,25 @@
       <c r="G39" s="15"/>
       <c r="H39" s="15"/>
     </row>
+    <row r="40" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B40" s="15"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="15"/>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A36:H36"/>
     <mergeCell ref="A37:H37"/>
     <mergeCell ref="A38:H38"/>
     <mergeCell ref="A39:H39"/>
+    <mergeCell ref="A40:H40"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4712,8 +5110,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:I42"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
@@ -4723,20 +5121,20 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>4</v>
@@ -4757,17 +5155,17 @@
         <v>9</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B6" s="17" t="n">
         <v>949</v>
@@ -4782,12 +5180,12 @@
         <v>1062</v>
       </c>
       <c r="I6" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7" s="17" t="n">
         <v>66</v>
@@ -4802,12 +5200,12 @@
         <v>66</v>
       </c>
       <c r="I7" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" s="17" t="n">
         <v>217</v>
@@ -4822,12 +5220,12 @@
         <v>240</v>
       </c>
       <c r="I8" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B9" s="17" t="n">
         <v>269</v>
@@ -4842,12 +5240,12 @@
         <v>291</v>
       </c>
       <c r="I9" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B10" s="17" t="n">
         <v>528</v>
@@ -4862,12 +5260,12 @@
         <v>598</v>
       </c>
       <c r="I10" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B11" s="17" t="n">
         <v>1015</v>
@@ -4882,41 +5280,41 @@
         <v>1129</v>
       </c>
       <c r="I11" s="18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B14" s="19" t="n">
         <f aca="false">(E11/B11)^(1/3)-1</f>
         <v>0.0361181940229247</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B15" s="19" t="n">
         <f aca="false">(E10/B10)^(1/3)-1</f>
         <v>0.0423712404969576</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F16" s="20" t="n">
         <f aca="false">$B$14</f>
@@ -4931,12 +5329,12 @@
         <v>0.0361181940229247</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F17" s="20" t="n">
         <f aca="false">$B$15</f>
@@ -4951,28 +5349,28 @@
         <v>0.0423712404969576</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B20" s="21" t="n">
         <v>102.6</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C21" s="22" t="n">
         <v>20</v>
@@ -4993,12 +5391,12 @@
         <v>0</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C22" s="17" t="n">
         <v>0</v>
@@ -5019,12 +5417,12 @@
         <v>15</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C23" s="17" t="n">
         <v>61</v>
@@ -5045,12 +5443,12 @@
         <v>61</v>
       </c>
       <c r="I23" s="18" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C24" s="22" t="n">
         <v>0</v>
@@ -5071,127 +5469,166 @@
         <v>0</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B27" s="23" t="n">
         <v>0.344</v>
       </c>
       <c r="I27" s="18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B28" s="17" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B29" s="17" t="n">
         <v>30</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B30" s="17" t="n">
         <v>100</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B31" s="17" t="n">
         <v>114</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B32" s="22" t="n">
         <v>225</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B34" s="22" t="n">
         <v>1500</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B35" s="24" t="n">
         <v>0.04</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B36" s="25" t="n">
         <v>7</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B37" s="22" t="n">
         <v>2000</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B40" s="26" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B41" s="21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B42" s="27" t="n">
+        <f aca="false">B40-B41</f>
+        <v>37.4</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -5211,7 +5648,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H48"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="0" width="12"/>
@@ -5219,20 +5656,20 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>4</v>
@@ -5254,315 +5691,315 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="B5" s="27" t="n">
+      <c r="A5" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="B5" s="29" t="n">
         <f aca="false">前提条件!B11</f>
         <v>1015</v>
       </c>
-      <c r="C5" s="27" t="n">
+      <c r="C5" s="29" t="n">
         <f aca="false">前提条件!C11</f>
         <v>1062</v>
       </c>
-      <c r="D5" s="27" t="n">
+      <c r="D5" s="29" t="n">
         <f aca="false">前提条件!D11</f>
         <v>1095</v>
       </c>
-      <c r="E5" s="27" t="n">
+      <c r="E5" s="29" t="n">
         <f aca="false">前提条件!E11</f>
         <v>1129</v>
       </c>
-      <c r="F5" s="28" t="n">
+      <c r="F5" s="30" t="n">
         <f aca="false">E5*(1+前提条件!F16)</f>
         <v>1169.77744105188</v>
       </c>
-      <c r="G5" s="28" t="n">
+      <c r="G5" s="30" t="n">
         <f aca="false">F5*(1+前提条件!G16)</f>
         <v>1212.02768963143</v>
       </c>
-      <c r="H5" s="28" t="n">
+      <c r="H5" s="30" t="n">
         <f aca="false">G5*(1+前提条件!H16)</f>
         <v>1255.8039408867</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C6" s="29" t="n">
+        <v>96</v>
+      </c>
+      <c r="C6" s="31" t="n">
         <f aca="false">C5/B5-1</f>
         <v>0.0463054187192118</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="31" t="n">
         <f aca="false">D5/C5-1</f>
         <v>0.0310734463276836</v>
       </c>
-      <c r="E6" s="29" t="n">
+      <c r="E6" s="31" t="n">
         <f aca="false">E5/D5-1</f>
         <v>0.0310502283105023</v>
       </c>
-      <c r="F6" s="29" t="n">
+      <c r="F6" s="31" t="n">
         <f aca="false">F5/E5-1</f>
         <v>0.0361181940229247</v>
       </c>
-      <c r="G6" s="29" t="n">
+      <c r="G6" s="31" t="n">
         <f aca="false">G5/F5-1</f>
         <v>0.0361181940229247</v>
       </c>
-      <c r="H6" s="29" t="n">
+      <c r="H6" s="31" t="n">
         <f aca="false">H5/G5-1</f>
         <v>0.0361181940229247</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="B7" s="30" t="n">
+        <v>97</v>
+      </c>
+      <c r="B7" s="32" t="n">
         <f aca="false">前提条件!B10</f>
         <v>528</v>
       </c>
-      <c r="C7" s="30" t="n">
+      <c r="C7" s="32" t="n">
         <f aca="false">前提条件!C10</f>
         <v>556</v>
       </c>
-      <c r="D7" s="30" t="n">
+      <c r="D7" s="32" t="n">
         <f aca="false">前提条件!D10</f>
         <v>576</v>
       </c>
-      <c r="E7" s="30" t="n">
+      <c r="E7" s="32" t="n">
         <f aca="false">前提条件!E10</f>
         <v>598</v>
       </c>
-      <c r="F7" s="31" t="n">
+      <c r="F7" s="33" t="n">
         <f aca="false">E7*(1+前提条件!F17)</f>
         <v>623.338001817181</v>
       </c>
-      <c r="G7" s="31" t="n">
+      <c r="G7" s="33" t="n">
         <f aca="false">F7*(1+前提条件!G17)</f>
         <v>649.749606203069</v>
       </c>
-      <c r="H7" s="31" t="n">
+      <c r="H7" s="33" t="n">
         <f aca="false">G7*(1+前提条件!H17)</f>
         <v>677.280303030303</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="B8" s="29" t="n">
+        <v>98</v>
+      </c>
+      <c r="B8" s="31" t="n">
         <f aca="false">B7/B5</f>
         <v>0.520197044334975</v>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="31" t="n">
         <f aca="false">IF(C5=0,0,C7/C5)</f>
         <v>0.523540489642185</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="31" t="n">
         <f aca="false">IF(D5=0,0,D7/D5)</f>
         <v>0.526027397260274</v>
       </c>
-      <c r="E8" s="29" t="n">
+      <c r="E8" s="31" t="n">
         <f aca="false">IF(E5=0,0,E7/E5)</f>
         <v>0.529672276350753</v>
       </c>
-      <c r="F8" s="29" t="n">
+      <c r="F8" s="31" t="n">
         <f aca="false">IF(F5=0,0,F7/F5)</f>
         <v>0.532868885945232</v>
       </c>
-      <c r="G8" s="29" t="n">
+      <c r="G8" s="31" t="n">
         <f aca="false">IF(G5=0,0,G7/G5)</f>
         <v>0.536084787304366</v>
       </c>
-      <c r="H8" s="29" t="n">
+      <c r="H8" s="31" t="n">
         <f aca="false">IF(H5=0,0,H7/H5)</f>
         <v>0.539320096855317</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C10" s="32" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" s="34" t="n">
         <f aca="false">前提条件!$B$20</f>
         <v>102.6</v>
       </c>
-      <c r="D10" s="32" t="n">
+      <c r="D10" s="34" t="n">
         <f aca="false">前提条件!$B$20</f>
         <v>102.6</v>
       </c>
-      <c r="E10" s="32" t="n">
+      <c r="E10" s="34" t="n">
         <f aca="false">前提条件!$B$20</f>
         <v>102.6</v>
       </c>
-      <c r="F10" s="32" t="n">
+      <c r="F10" s="34" t="n">
         <f aca="false">前提条件!$B$20</f>
         <v>102.6</v>
       </c>
-      <c r="G10" s="32" t="n">
+      <c r="G10" s="34" t="n">
         <f aca="false">前提条件!$B$20</f>
         <v>102.6</v>
       </c>
-      <c r="H10" s="32" t="n">
+      <c r="H10" s="34" t="n">
         <f aca="false">前提条件!$B$20</f>
         <v>102.6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C11" s="33" t="n">
+        <v>101</v>
+      </c>
+      <c r="C11" s="35" t="n">
         <f aca="false">-前提条件!C21</f>
         <v>-20</v>
       </c>
-      <c r="D11" s="33" t="n">
+      <c r="D11" s="35" t="n">
         <f aca="false">-前提条件!D21</f>
         <v>-20</v>
       </c>
-      <c r="E11" s="33" t="n">
+      <c r="E11" s="35" t="n">
         <f aca="false">-前提条件!E21</f>
         <v>-20</v>
       </c>
-      <c r="F11" s="33" t="n">
+      <c r="F11" s="35" t="n">
         <f aca="false">-前提条件!F21</f>
         <v>-0</v>
       </c>
-      <c r="G11" s="33" t="n">
+      <c r="G11" s="35" t="n">
         <f aca="false">-前提条件!G21</f>
         <v>-0</v>
       </c>
-      <c r="H11" s="33" t="n">
+      <c r="H11" s="35" t="n">
         <f aca="false">-前提条件!H21</f>
         <v>-0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C12" s="33" t="n">
+        <v>102</v>
+      </c>
+      <c r="C12" s="35" t="n">
         <f aca="false">-前提条件!C22</f>
         <v>-0</v>
       </c>
-      <c r="D12" s="33" t="n">
+      <c r="D12" s="35" t="n">
         <f aca="false">-前提条件!D22</f>
         <v>-15</v>
       </c>
-      <c r="E12" s="33" t="n">
+      <c r="E12" s="35" t="n">
         <f aca="false">-前提条件!E22</f>
         <v>-15</v>
       </c>
-      <c r="F12" s="33" t="n">
+      <c r="F12" s="35" t="n">
         <f aca="false">-前提条件!F22</f>
         <v>-15</v>
       </c>
-      <c r="G12" s="33" t="n">
+      <c r="G12" s="35" t="n">
         <f aca="false">-前提条件!G22</f>
         <v>-15</v>
       </c>
-      <c r="H12" s="33" t="n">
+      <c r="H12" s="35" t="n">
         <f aca="false">-前提条件!H22</f>
         <v>-15</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C13" s="33" t="n">
+        <v>103</v>
+      </c>
+      <c r="C13" s="35" t="n">
         <f aca="false">-前提条件!C23</f>
         <v>-61</v>
       </c>
-      <c r="D13" s="33" t="n">
+      <c r="D13" s="35" t="n">
         <f aca="false">-前提条件!D23</f>
         <v>-61</v>
       </c>
-      <c r="E13" s="33" t="n">
+      <c r="E13" s="35" t="n">
         <f aca="false">-前提条件!E23</f>
         <v>-61</v>
       </c>
-      <c r="F13" s="33" t="n">
+      <c r="F13" s="35" t="n">
         <f aca="false">-前提条件!F23</f>
         <v>-61</v>
       </c>
-      <c r="G13" s="33" t="n">
+      <c r="G13" s="35" t="n">
         <f aca="false">-前提条件!G23</f>
         <v>-61</v>
       </c>
-      <c r="H13" s="33" t="n">
+      <c r="H13" s="35" t="n">
         <f aca="false">-前提条件!H23</f>
         <v>-61</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C14" s="33" t="n">
+        <v>104</v>
+      </c>
+      <c r="C14" s="35" t="n">
         <f aca="false">-前提条件!C24</f>
         <v>-0</v>
       </c>
-      <c r="D14" s="33" t="n">
+      <c r="D14" s="35" t="n">
         <f aca="false">-前提条件!D24</f>
         <v>-0</v>
       </c>
-      <c r="E14" s="33" t="n">
+      <c r="E14" s="35" t="n">
         <f aca="false">-前提条件!E24</f>
         <v>-0</v>
       </c>
-      <c r="F14" s="33" t="n">
+      <c r="F14" s="35" t="n">
         <f aca="false">-前提条件!F24</f>
         <v>-400</v>
       </c>
-      <c r="G14" s="33" t="n">
+      <c r="G14" s="35" t="n">
         <f aca="false">-前提条件!G24</f>
         <v>-400</v>
       </c>
-      <c r="H14" s="33" t="n">
+      <c r="H14" s="35" t="n">
         <f aca="false">-前提条件!H24</f>
         <v>-0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="C15" s="34" t="n">
+      <c r="A15" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="C15" s="36" t="n">
         <f aca="false">SUM(C7,C10:C14)</f>
         <v>577.6</v>
       </c>
-      <c r="D15" s="34" t="n">
+      <c r="D15" s="36" t="n">
         <f aca="false">SUM(D7,D10:D14)</f>
         <v>582.6</v>
       </c>
-      <c r="E15" s="34" t="n">
+      <c r="E15" s="36" t="n">
         <f aca="false">SUM(E7,E10:E14)</f>
         <v>604.6</v>
       </c>
-      <c r="F15" s="34" t="n">
+      <c r="F15" s="36" t="n">
         <f aca="false">SUM(F7,F10:F14)</f>
         <v>249.938001817181</v>
       </c>
-      <c r="G15" s="34" t="n">
+      <c r="G15" s="36" t="n">
         <f aca="false">SUM(G7,G10:G14)</f>
         <v>276.349606203069</v>
       </c>
-      <c r="H15" s="34" t="n">
+      <c r="H15" s="36" t="n">
         <f aca="false">SUM(H7,H10:H14)</f>
         <v>703.880303030303</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C16" s="7" t="n">
         <f aca="false">前提条件!$B$28</f>
@@ -5591,684 +6028,684 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="C17" s="35" t="n">
+        <v>107</v>
+      </c>
+      <c r="C17" s="37" t="n">
         <f aca="false">C15-C16</f>
         <v>577.6</v>
       </c>
-      <c r="D17" s="35" t="n">
+      <c r="D17" s="37" t="n">
         <f aca="false">D15-D16</f>
         <v>582.6</v>
       </c>
-      <c r="E17" s="35" t="n">
+      <c r="E17" s="37" t="n">
         <f aca="false">E15-E16</f>
         <v>604.6</v>
       </c>
-      <c r="F17" s="35" t="n">
+      <c r="F17" s="37" t="n">
         <f aca="false">F15-F16</f>
         <v>249.938001817181</v>
       </c>
-      <c r="G17" s="35" t="n">
+      <c r="G17" s="37" t="n">
         <f aca="false">G15-G16</f>
         <v>276.349606203069</v>
       </c>
-      <c r="H17" s="35" t="n">
+      <c r="H17" s="37" t="n">
         <f aca="false">H15-H16</f>
         <v>703.880303030303</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C18" s="36" t="n">
+        <v>108</v>
+      </c>
+      <c r="C18" s="38" t="n">
         <f aca="false">C35*前提条件!$B$35</f>
         <v>60</v>
       </c>
-      <c r="D18" s="36" t="n">
+      <c r="D18" s="38" t="n">
         <f aca="false">D35*前提条件!$B$35</f>
         <v>52.4034232776298</v>
       </c>
-      <c r="E18" s="36" t="n">
+      <c r="E18" s="38" t="n">
         <f aca="false">E35*前提条件!$B$35</f>
         <v>44.5029834863647</v>
       </c>
-      <c r="F18" s="36" t="n">
+      <c r="F18" s="38" t="n">
         <f aca="false">F35*前提条件!$B$35</f>
         <v>36.286526103449</v>
       </c>
-      <c r="G18" s="36" t="n">
+      <c r="G18" s="38" t="n">
         <f aca="false">G35*前提条件!$B$35</f>
         <v>27.7414104252167</v>
       </c>
-      <c r="H18" s="36" t="n">
+      <c r="H18" s="38" t="n">
         <f aca="false">H35*前提条件!$B$35</f>
         <v>18.8544901198551</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C19" s="36" t="n">
+        <v>109</v>
+      </c>
+      <c r="C19" s="38" t="n">
         <f aca="false">C17-C18</f>
         <v>517.6</v>
       </c>
-      <c r="D19" s="36" t="n">
+      <c r="D19" s="38" t="n">
         <f aca="false">D17-D18</f>
         <v>530.19657672237</v>
       </c>
-      <c r="E19" s="36" t="n">
+      <c r="E19" s="38" t="n">
         <f aca="false">E17-E18</f>
         <v>560.097016513635</v>
       </c>
-      <c r="F19" s="36" t="n">
+      <c r="F19" s="38" t="n">
         <f aca="false">F17-F18</f>
         <v>213.651475713732</v>
       </c>
-      <c r="G19" s="36" t="n">
+      <c r="G19" s="38" t="n">
         <f aca="false">G17-G18</f>
         <v>248.608195777853</v>
       </c>
-      <c r="H19" s="36" t="n">
+      <c r="H19" s="38" t="n">
         <f aca="false">H17-H18</f>
         <v>685.025812910448</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C20" s="36" t="n">
+        <v>110</v>
+      </c>
+      <c r="C20" s="38" t="n">
         <f aca="false">MAX(0,C19)*前提条件!$B$27</f>
         <v>178.0544</v>
       </c>
-      <c r="D20" s="36" t="n">
+      <c r="D20" s="38" t="n">
         <f aca="false">MAX(0,D19)*前提条件!$B$27</f>
         <v>182.387622392495</v>
       </c>
-      <c r="E20" s="36" t="n">
+      <c r="E20" s="38" t="n">
         <f aca="false">MAX(0,E19)*前提条件!$B$27</f>
         <v>192.673373680691</v>
       </c>
-      <c r="F20" s="36" t="n">
+      <c r="F20" s="38" t="n">
         <f aca="false">MAX(0,F19)*前提条件!$B$27</f>
         <v>73.4961076455237</v>
       </c>
-      <c r="G20" s="36" t="n">
+      <c r="G20" s="38" t="n">
         <f aca="false">MAX(0,G19)*前提条件!$B$27</f>
         <v>85.5212193475813</v>
       </c>
-      <c r="H20" s="36" t="n">
+      <c r="H20" s="38" t="n">
         <f aca="false">MAX(0,H19)*前提条件!$B$27</f>
         <v>235.648879641194</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="26" t="s">
+      <c r="A21" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="34" t="n">
+      <c r="C21" s="36" t="n">
         <f aca="false">C19-C20</f>
         <v>339.5456</v>
       </c>
-      <c r="D21" s="34" t="n">
+      <c r="D21" s="36" t="n">
         <f aca="false">D19-D20</f>
         <v>347.808954329875</v>
       </c>
-      <c r="E21" s="34" t="n">
+      <c r="E21" s="36" t="n">
         <f aca="false">E19-E20</f>
         <v>367.423642832945</v>
       </c>
-      <c r="F21" s="34" t="n">
+      <c r="F21" s="36" t="n">
         <f aca="false">F19-F20</f>
         <v>140.155368068208</v>
       </c>
-      <c r="G21" s="34" t="n">
+      <c r="G21" s="36" t="n">
         <f aca="false">G19-G20</f>
         <v>163.086976430271</v>
       </c>
-      <c r="H21" s="34" t="n">
+      <c r="H21" s="36" t="n">
         <f aca="false">H19-H20</f>
         <v>449.376933269254</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="36" t="n">
+      <c r="C24" s="38" t="n">
         <f aca="false">C21</f>
         <v>339.5456</v>
       </c>
-      <c r="D24" s="36" t="n">
+      <c r="D24" s="38" t="n">
         <f aca="false">D21</f>
         <v>347.808954329875</v>
       </c>
-      <c r="E24" s="36" t="n">
+      <c r="E24" s="38" t="n">
         <f aca="false">E21</f>
         <v>367.423642832945</v>
       </c>
-      <c r="F24" s="36" t="n">
+      <c r="F24" s="38" t="n">
         <f aca="false">F21</f>
         <v>140.155368068208</v>
       </c>
-      <c r="G24" s="36" t="n">
+      <c r="G24" s="38" t="n">
         <f aca="false">G21</f>
         <v>163.086976430271</v>
       </c>
-      <c r="H24" s="36" t="n">
+      <c r="H24" s="38" t="n">
         <f aca="false">H21</f>
         <v>449.376933269254</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C25" s="33" t="n">
+        <v>106</v>
+      </c>
+      <c r="C25" s="35" t="n">
         <f aca="false">C16</f>
         <v>0</v>
       </c>
-      <c r="D25" s="33" t="n">
+      <c r="D25" s="35" t="n">
         <f aca="false">D16</f>
         <v>0</v>
       </c>
-      <c r="E25" s="33" t="n">
+      <c r="E25" s="35" t="n">
         <f aca="false">E16</f>
         <v>0</v>
       </c>
-      <c r="F25" s="33" t="n">
+      <c r="F25" s="35" t="n">
         <f aca="false">F16</f>
         <v>0</v>
       </c>
-      <c r="G25" s="33" t="n">
+      <c r="G25" s="35" t="n">
         <f aca="false">G16</f>
         <v>0</v>
       </c>
-      <c r="H25" s="33" t="n">
+      <c r="H25" s="35" t="n">
         <f aca="false">H16</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C26" s="33" t="n">
+        <v>112</v>
+      </c>
+      <c r="C26" s="35" t="n">
         <f aca="false">-前提条件!$B$29</f>
         <v>-30</v>
       </c>
-      <c r="D26" s="33" t="n">
+      <c r="D26" s="35" t="n">
         <f aca="false">-前提条件!$B$29</f>
         <v>-30</v>
       </c>
-      <c r="E26" s="33" t="n">
+      <c r="E26" s="35" t="n">
         <f aca="false">-前提条件!$B$29</f>
         <v>-30</v>
       </c>
-      <c r="F26" s="33" t="n">
+      <c r="F26" s="35" t="n">
         <f aca="false">-前提条件!$B$29</f>
         <v>-30</v>
       </c>
-      <c r="G26" s="33" t="n">
+      <c r="G26" s="35" t="n">
         <f aca="false">-前提条件!$B$29</f>
         <v>-30</v>
       </c>
-      <c r="H26" s="33" t="n">
+      <c r="H26" s="35" t="n">
         <f aca="false">-前提条件!$B$29</f>
         <v>-30</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="C27" s="36" t="n">
+        <v>113</v>
+      </c>
+      <c r="C27" s="38" t="n">
         <f aca="false">-(前提条件!B31-前提条件!B32*前提条件!B27)</f>
         <v>-36.6</v>
       </c>
-      <c r="D27" s="36" t="n">
+      <c r="D27" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="E27" s="36" t="n">
+      <c r="E27" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="F27" s="36" t="n">
+      <c r="F27" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="G27" s="36" t="n">
+      <c r="G27" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="36" t="n">
+      <c r="H27" s="38" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="C28" s="35" t="n">
+        <v>114</v>
+      </c>
+      <c r="C28" s="37" t="n">
         <f aca="false">SUM(C24:C27)</f>
         <v>272.9456</v>
       </c>
-      <c r="D28" s="35" t="n">
+      <c r="D28" s="37" t="n">
         <f aca="false">SUM(D24:D27)</f>
         <v>317.808954329875</v>
       </c>
-      <c r="E28" s="35" t="n">
+      <c r="E28" s="37" t="n">
         <f aca="false">SUM(E24:E27)</f>
         <v>337.423642832945</v>
       </c>
-      <c r="F28" s="35" t="n">
+      <c r="F28" s="37" t="n">
         <f aca="false">SUM(F24:F27)</f>
         <v>110.155368068208</v>
       </c>
-      <c r="G28" s="35" t="n">
+      <c r="G28" s="37" t="n">
         <f aca="false">SUM(G24:G27)</f>
         <v>133.086976430271</v>
       </c>
-      <c r="H28" s="35" t="n">
+      <c r="H28" s="37" t="n">
         <f aca="false">SUM(H24:H27)</f>
         <v>419.376933269254</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C29" s="36" t="n">
+        <v>115</v>
+      </c>
+      <c r="C29" s="38" t="n">
         <f aca="false">-C38</f>
         <v>-189.914418059256</v>
       </c>
-      <c r="D29" s="36" t="n">
+      <c r="D29" s="38" t="n">
         <f aca="false">-D38</f>
         <v>-197.510994781627</v>
       </c>
-      <c r="E29" s="36" t="n">
+      <c r="E29" s="38" t="n">
         <f aca="false">-E38</f>
         <v>-205.411434572892</v>
       </c>
-      <c r="F29" s="36" t="n">
+      <c r="F29" s="38" t="n">
         <f aca="false">-F38</f>
         <v>-213.627891955807</v>
       </c>
-      <c r="G29" s="36" t="n">
+      <c r="G29" s="38" t="n">
         <f aca="false">-G38</f>
         <v>-222.17300763404</v>
       </c>
-      <c r="H29" s="36" t="n">
+      <c r="H29" s="38" t="n">
         <f aca="false">-H38</f>
         <v>-231.059927939401</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="26" t="s">
-        <v>108</v>
-      </c>
-      <c r="C30" s="34" t="n">
+      <c r="A30" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="C30" s="36" t="n">
         <f aca="false">C28+C29</f>
         <v>83.0311819407436</v>
       </c>
-      <c r="D30" s="34" t="n">
+      <c r="D30" s="36" t="n">
         <f aca="false">D28+D29</f>
         <v>120.297959548248</v>
       </c>
-      <c r="E30" s="34" t="n">
+      <c r="E30" s="36" t="n">
         <f aca="false">E28+E29</f>
         <v>132.012208260053</v>
       </c>
-      <c r="F30" s="34" t="n">
+      <c r="F30" s="36" t="n">
         <f aca="false">F28+F29</f>
         <v>-103.472523887599</v>
       </c>
-      <c r="G30" s="34" t="n">
+      <c r="G30" s="36" t="n">
         <f aca="false">G28+G29</f>
         <v>-89.0860312037683</v>
       </c>
-      <c r="H30" s="34" t="n">
+      <c r="H30" s="36" t="n">
         <f aca="false">H28+H29</f>
         <v>188.317005329853</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" s="35" t="n">
-        <f aca="false">前提条件!B30+C30</f>
-        <v>183.031181940744</v>
-      </c>
-      <c r="D31" s="35" t="n">
+        <v>117</v>
+      </c>
+      <c r="C31" s="37" t="n">
+        <f aca="false">前提条件!B30+前提条件!B42+C30</f>
+        <v>220.431181940744</v>
+      </c>
+      <c r="D31" s="37" t="n">
         <f aca="false">C31+D30</f>
-        <v>303.329141488992</v>
-      </c>
-      <c r="E31" s="35" t="n">
+        <v>340.729141488992</v>
+      </c>
+      <c r="E31" s="37" t="n">
         <f aca="false">D31+E30</f>
-        <v>435.341349749045</v>
-      </c>
-      <c r="F31" s="35" t="n">
+        <v>472.741349749045</v>
+      </c>
+      <c r="F31" s="37" t="n">
         <f aca="false">E31+F30</f>
-        <v>331.868825861446</v>
-      </c>
-      <c r="G31" s="35" t="n">
+        <v>369.268825861446</v>
+      </c>
+      <c r="G31" s="37" t="n">
         <f aca="false">F31+G30</f>
-        <v>242.782794657677</v>
-      </c>
-      <c r="H31" s="35" t="n">
+        <v>280.182794657677</v>
+      </c>
+      <c r="H31" s="37" t="n">
         <f aca="false">G31+H30</f>
-        <v>431.09979998753</v>
+        <v>468.49979998753</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C35" s="32" t="n">
+        <v>119</v>
+      </c>
+      <c r="C35" s="34" t="n">
         <f aca="false">前提条件!B34</f>
         <v>1500</v>
       </c>
-      <c r="D35" s="36" t="n">
+      <c r="D35" s="38" t="n">
         <f aca="false">C39</f>
         <v>1310.08558194074</v>
       </c>
-      <c r="E35" s="36" t="n">
+      <c r="E35" s="38" t="n">
         <f aca="false">D39</f>
         <v>1112.57458715912</v>
       </c>
-      <c r="F35" s="36" t="n">
+      <c r="F35" s="38" t="n">
         <f aca="false">E39</f>
         <v>907.163152586225</v>
       </c>
-      <c r="G35" s="36" t="n">
+      <c r="G35" s="38" t="n">
         <f aca="false">F39</f>
         <v>693.535260630418</v>
       </c>
-      <c r="H35" s="36" t="n">
+      <c r="H35" s="38" t="n">
         <f aca="false">G39</f>
         <v>471.362252996378</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C36" s="36" t="n">
+        <v>120</v>
+      </c>
+      <c r="C36" s="38" t="n">
         <f aca="false">IF(C35&lt;=0.001,0,-PMT(前提条件!$B$35,前提条件!$B$36,前提条件!$B$34))</f>
         <v>249.914418059256</v>
       </c>
-      <c r="D36" s="36" t="n">
+      <c r="D36" s="38" t="n">
         <f aca="false">IF(D35&lt;=0.001,0,-PMT(前提条件!$B$35,前提条件!$B$36,前提条件!$B$34))</f>
         <v>249.914418059256</v>
       </c>
-      <c r="E36" s="36" t="n">
+      <c r="E36" s="38" t="n">
         <f aca="false">IF(E35&lt;=0.001,0,-PMT(前提条件!$B$35,前提条件!$B$36,前提条件!$B$34))</f>
         <v>249.914418059256</v>
       </c>
-      <c r="F36" s="36" t="n">
+      <c r="F36" s="38" t="n">
         <f aca="false">IF(F35&lt;=0.001,0,-PMT(前提条件!$B$35,前提条件!$B$36,前提条件!$B$34))</f>
         <v>249.914418059256</v>
       </c>
-      <c r="G36" s="36" t="n">
+      <c r="G36" s="38" t="n">
         <f aca="false">IF(G35&lt;=0.001,0,-PMT(前提条件!$B$35,前提条件!$B$36,前提条件!$B$34))</f>
         <v>249.914418059256</v>
       </c>
-      <c r="H36" s="36" t="n">
+      <c r="H36" s="38" t="n">
         <f aca="false">IF(H35&lt;=0.001,0,-PMT(前提条件!$B$35,前提条件!$B$36,前提条件!$B$34))</f>
         <v>249.914418059256</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="C37" s="36" t="n">
+        <v>121</v>
+      </c>
+      <c r="C37" s="38" t="n">
         <f aca="false">C18</f>
         <v>60</v>
       </c>
-      <c r="D37" s="36" t="n">
+      <c r="D37" s="38" t="n">
         <f aca="false">D18</f>
         <v>52.4034232776298</v>
       </c>
-      <c r="E37" s="36" t="n">
+      <c r="E37" s="38" t="n">
         <f aca="false">E18</f>
         <v>44.5029834863647</v>
       </c>
-      <c r="F37" s="36" t="n">
+      <c r="F37" s="38" t="n">
         <f aca="false">F18</f>
         <v>36.286526103449</v>
       </c>
-      <c r="G37" s="36" t="n">
+      <c r="G37" s="38" t="n">
         <f aca="false">G18</f>
         <v>27.7414104252167</v>
       </c>
-      <c r="H37" s="36" t="n">
+      <c r="H37" s="38" t="n">
         <f aca="false">H18</f>
         <v>18.8544901198551</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C38" s="36" t="n">
+        <v>122</v>
+      </c>
+      <c r="C38" s="38" t="n">
         <f aca="false">MIN(C35,C36-C37)</f>
         <v>189.914418059256</v>
       </c>
-      <c r="D38" s="36" t="n">
+      <c r="D38" s="38" t="n">
         <f aca="false">MIN(D35,D36-D37)</f>
         <v>197.510994781627</v>
       </c>
-      <c r="E38" s="36" t="n">
+      <c r="E38" s="38" t="n">
         <f aca="false">MIN(E35,E36-E37)</f>
         <v>205.411434572892</v>
       </c>
-      <c r="F38" s="36" t="n">
+      <c r="F38" s="38" t="n">
         <f aca="false">MIN(F35,F36-F37)</f>
         <v>213.627891955807</v>
       </c>
-      <c r="G38" s="36" t="n">
+      <c r="G38" s="38" t="n">
         <f aca="false">MIN(G35,G36-G37)</f>
         <v>222.17300763404</v>
       </c>
-      <c r="H38" s="36" t="n">
+      <c r="H38" s="38" t="n">
         <f aca="false">MIN(H35,H36-H37)</f>
         <v>231.059927939401</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="C39" s="35" t="n">
+        <v>123</v>
+      </c>
+      <c r="C39" s="37" t="n">
         <f aca="false">C35-C38</f>
         <v>1310.08558194074</v>
       </c>
-      <c r="D39" s="35" t="n">
+      <c r="D39" s="37" t="n">
         <f aca="false">D35-D38</f>
         <v>1112.57458715912</v>
       </c>
-      <c r="E39" s="35" t="n">
+      <c r="E39" s="37" t="n">
         <f aca="false">E35-E38</f>
         <v>907.163152586225</v>
       </c>
-      <c r="F39" s="35" t="n">
+      <c r="F39" s="37" t="n">
         <f aca="false">F35-F38</f>
         <v>693.535260630418</v>
       </c>
-      <c r="G39" s="35" t="n">
+      <c r="G39" s="37" t="n">
         <f aca="false">G35-G38</f>
         <v>471.362252996378</v>
       </c>
-      <c r="H39" s="35" t="n">
+      <c r="H39" s="37" t="n">
         <f aca="false">H35-H38</f>
         <v>240.302325056977</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="37" t="s">
-        <v>115</v>
-      </c>
-      <c r="C40" s="38" t="n">
+      <c r="A40" s="39" t="s">
+        <v>124</v>
+      </c>
+      <c r="C40" s="40" t="n">
         <f aca="false">IF(C36=0,0,(C15-C20-前提条件!$B$29)/C36)</f>
         <v>1.47868859615926</v>
       </c>
-      <c r="D40" s="38" t="n">
+      <c r="D40" s="40" t="n">
         <f aca="false">IF(D36=0,0,(D15-D20-前提条件!$B$29)/D36)</f>
         <v>1.48135661992789</v>
       </c>
-      <c r="E40" s="38" t="n">
+      <c r="E40" s="40" t="n">
         <f aca="false">IF(E36=0,0,(E15-E20-前提条件!$B$29)/E36)</f>
         <v>1.5282296607183</v>
       </c>
-      <c r="F40" s="38" t="n">
+      <c r="F40" s="40" t="n">
         <f aca="false">IF(F36=0,0,(F15-F20-前提条件!$B$29)/F36)</f>
         <v>0.58596816985939</v>
       </c>
-      <c r="G40" s="38" t="n">
+      <c r="G40" s="40" t="n">
         <f aca="false">IF(G36=0,0,(G15-G20-前提条件!$B$29)/G36)</f>
         <v>0.643533846924168</v>
       </c>
-      <c r="H40" s="38" t="n">
+      <c r="H40" s="40" t="n">
         <f aca="false">IF(H36=0,0,(H15-H20-前提条件!$B$29)/H36)</f>
         <v>1.7535259741805</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="18" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="11" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="C44" s="36" t="n">
+        <v>127</v>
+      </c>
+      <c r="C44" s="38" t="n">
         <f aca="false">前提条件!B32*前提条件!B27</f>
         <v>77.4</v>
       </c>
-      <c r="D44" s="36" t="n">
+      <c r="D44" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="E44" s="36" t="n">
+      <c r="E44" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="F44" s="36" t="n">
+      <c r="F44" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="G44" s="36" t="n">
+      <c r="G44" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="H44" s="36" t="n">
+      <c r="H44" s="38" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="C45" s="36" t="n">
+        <v>128</v>
+      </c>
+      <c r="C45" s="38" t="n">
         <f aca="false">-C14*前提条件!$B$27</f>
         <v>0</v>
       </c>
-      <c r="D45" s="36" t="n">
+      <c r="D45" s="38" t="n">
         <f aca="false">-D14*前提条件!$B$27</f>
         <v>0</v>
       </c>
-      <c r="E45" s="36" t="n">
+      <c r="E45" s="38" t="n">
         <f aca="false">-E14*前提条件!$B$27</f>
         <v>0</v>
       </c>
-      <c r="F45" s="36" t="n">
+      <c r="F45" s="38" t="n">
         <f aca="false">-F14*前提条件!$B$27</f>
         <v>137.6</v>
       </c>
-      <c r="G45" s="36" t="n">
+      <c r="G45" s="38" t="n">
         <f aca="false">-G14*前提条件!$B$27</f>
         <v>137.6</v>
       </c>
-      <c r="H45" s="36" t="n">
+      <c r="H45" s="38" t="n">
         <f aca="false">-H14*前提条件!$B$27</f>
         <v>0</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="C46" s="35" t="n">
+        <v>129</v>
+      </c>
+      <c r="C46" s="37" t="n">
         <f aca="false">C44+C45</f>
         <v>77.4</v>
       </c>
-      <c r="D46" s="35" t="n">
+      <c r="D46" s="37" t="n">
         <f aca="false">D44+D45</f>
         <v>0</v>
       </c>
-      <c r="E46" s="35" t="n">
+      <c r="E46" s="37" t="n">
         <f aca="false">E44+E45</f>
         <v>0</v>
       </c>
-      <c r="F46" s="35" t="n">
+      <c r="F46" s="37" t="n">
         <f aca="false">F44+F45</f>
         <v>137.6</v>
       </c>
-      <c r="G46" s="35" t="n">
+      <c r="G46" s="37" t="n">
         <f aca="false">G44+G45</f>
         <v>137.6</v>
       </c>
-      <c r="H46" s="35" t="n">
+      <c r="H46" s="37" t="n">
         <f aca="false">H44+H45</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="26" t="s">
-        <v>121</v>
-      </c>
-      <c r="C47" s="34" t="n">
+      <c r="A47" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="C47" s="36" t="n">
         <f aca="false">C46</f>
         <v>77.4</v>
       </c>
-      <c r="D47" s="34" t="n">
+      <c r="D47" s="36" t="n">
         <f aca="false">C47+D46</f>
         <v>77.4</v>
       </c>
-      <c r="E47" s="34" t="n">
+      <c r="E47" s="36" t="n">
         <f aca="false">D47+E46</f>
         <v>77.4</v>
       </c>
-      <c r="F47" s="34" t="n">
+      <c r="F47" s="36" t="n">
         <f aca="false">E47+F46</f>
         <v>215</v>
       </c>
-      <c r="G47" s="34" t="n">
+      <c r="G47" s="36" t="n">
         <f aca="false">F47+G46</f>
         <v>352.6</v>
       </c>
-      <c r="H47" s="34" t="n">
+      <c r="H47" s="36" t="n">
         <f aca="false">G47+H46</f>
         <v>352.6</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -6288,7 +6725,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H48"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="0" width="12"/>
@@ -6296,20 +6733,20 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>4</v>
@@ -6331,315 +6768,315 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="B5" s="27" t="n">
+      <c r="A5" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="B5" s="29" t="n">
         <f aca="false">前提条件!B11</f>
         <v>1015</v>
       </c>
-      <c r="C5" s="27" t="n">
+      <c r="C5" s="29" t="n">
         <f aca="false">前提条件!C11</f>
         <v>1062</v>
       </c>
-      <c r="D5" s="27" t="n">
+      <c r="D5" s="29" t="n">
         <f aca="false">前提条件!D11</f>
         <v>1095</v>
       </c>
-      <c r="E5" s="27" t="n">
+      <c r="E5" s="29" t="n">
         <f aca="false">前提条件!E11</f>
         <v>1129</v>
       </c>
-      <c r="F5" s="28" t="n">
+      <c r="F5" s="30" t="n">
         <f aca="false">E5*(1+前提条件!F16)</f>
         <v>1169.77744105188</v>
       </c>
-      <c r="G5" s="28" t="n">
+      <c r="G5" s="30" t="n">
         <f aca="false">F5*(1+前提条件!G16)</f>
         <v>1212.02768963143</v>
       </c>
-      <c r="H5" s="28" t="n">
+      <c r="H5" s="30" t="n">
         <f aca="false">G5*(1+前提条件!H16)</f>
         <v>1255.8039408867</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C6" s="29" t="n">
+        <v>96</v>
+      </c>
+      <c r="C6" s="31" t="n">
         <f aca="false">C5/B5-1</f>
         <v>0.0463054187192118</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="31" t="n">
         <f aca="false">D5/C5-1</f>
         <v>0.0310734463276836</v>
       </c>
-      <c r="E6" s="29" t="n">
+      <c r="E6" s="31" t="n">
         <f aca="false">E5/D5-1</f>
         <v>0.0310502283105023</v>
       </c>
-      <c r="F6" s="29" t="n">
+      <c r="F6" s="31" t="n">
         <f aca="false">F5/E5-1</f>
         <v>0.0361181940229247</v>
       </c>
-      <c r="G6" s="29" t="n">
+      <c r="G6" s="31" t="n">
         <f aca="false">G5/F5-1</f>
         <v>0.0361181940229247</v>
       </c>
-      <c r="H6" s="29" t="n">
+      <c r="H6" s="31" t="n">
         <f aca="false">H5/G5-1</f>
         <v>0.0361181940229247</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="B7" s="30" t="n">
+        <v>97</v>
+      </c>
+      <c r="B7" s="32" t="n">
         <f aca="false">前提条件!B10</f>
         <v>528</v>
       </c>
-      <c r="C7" s="30" t="n">
+      <c r="C7" s="32" t="n">
         <f aca="false">前提条件!C10</f>
         <v>556</v>
       </c>
-      <c r="D7" s="30" t="n">
+      <c r="D7" s="32" t="n">
         <f aca="false">前提条件!D10</f>
         <v>576</v>
       </c>
-      <c r="E7" s="30" t="n">
+      <c r="E7" s="32" t="n">
         <f aca="false">前提条件!E10</f>
         <v>598</v>
       </c>
-      <c r="F7" s="31" t="n">
+      <c r="F7" s="33" t="n">
         <f aca="false">E7*(1+前提条件!F17)</f>
         <v>623.338001817181</v>
       </c>
-      <c r="G7" s="31" t="n">
+      <c r="G7" s="33" t="n">
         <f aca="false">F7*(1+前提条件!G17)</f>
         <v>649.749606203069</v>
       </c>
-      <c r="H7" s="31" t="n">
+      <c r="H7" s="33" t="n">
         <f aca="false">G7*(1+前提条件!H17)</f>
         <v>677.280303030303</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="B8" s="29" t="n">
+        <v>98</v>
+      </c>
+      <c r="B8" s="31" t="n">
         <f aca="false">B7/B5</f>
         <v>0.520197044334975</v>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="31" t="n">
         <f aca="false">IF(C5=0,0,C7/C5)</f>
         <v>0.523540489642185</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="31" t="n">
         <f aca="false">IF(D5=0,0,D7/D5)</f>
         <v>0.526027397260274</v>
       </c>
-      <c r="E8" s="29" t="n">
+      <c r="E8" s="31" t="n">
         <f aca="false">IF(E5=0,0,E7/E5)</f>
         <v>0.529672276350753</v>
       </c>
-      <c r="F8" s="29" t="n">
+      <c r="F8" s="31" t="n">
         <f aca="false">IF(F5=0,0,F7/F5)</f>
         <v>0.532868885945232</v>
       </c>
-      <c r="G8" s="29" t="n">
+      <c r="G8" s="31" t="n">
         <f aca="false">IF(G5=0,0,G7/G5)</f>
         <v>0.536084787304366</v>
       </c>
-      <c r="H8" s="29" t="n">
+      <c r="H8" s="31" t="n">
         <f aca="false">IF(H5=0,0,H7/H5)</f>
         <v>0.539320096855317</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C10" s="32" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" s="34" t="n">
         <f aca="false">前提条件!$B$20</f>
         <v>102.6</v>
       </c>
-      <c r="D10" s="32" t="n">
+      <c r="D10" s="34" t="n">
         <f aca="false">前提条件!$B$20</f>
         <v>102.6</v>
       </c>
-      <c r="E10" s="32" t="n">
+      <c r="E10" s="34" t="n">
         <f aca="false">前提条件!$B$20</f>
         <v>102.6</v>
       </c>
-      <c r="F10" s="32" t="n">
+      <c r="F10" s="34" t="n">
         <f aca="false">前提条件!$B$20</f>
         <v>102.6</v>
       </c>
-      <c r="G10" s="32" t="n">
+      <c r="G10" s="34" t="n">
         <f aca="false">前提条件!$B$20</f>
         <v>102.6</v>
       </c>
-      <c r="H10" s="32" t="n">
+      <c r="H10" s="34" t="n">
         <f aca="false">前提条件!$B$20</f>
         <v>102.6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C11" s="33" t="n">
+        <v>101</v>
+      </c>
+      <c r="C11" s="35" t="n">
         <f aca="false">-前提条件!C21</f>
         <v>-20</v>
       </c>
-      <c r="D11" s="33" t="n">
+      <c r="D11" s="35" t="n">
         <f aca="false">-前提条件!D21</f>
         <v>-20</v>
       </c>
-      <c r="E11" s="33" t="n">
+      <c r="E11" s="35" t="n">
         <f aca="false">-前提条件!E21</f>
         <v>-20</v>
       </c>
-      <c r="F11" s="33" t="n">
+      <c r="F11" s="35" t="n">
         <f aca="false">-前提条件!F21</f>
         <v>-0</v>
       </c>
-      <c r="G11" s="33" t="n">
+      <c r="G11" s="35" t="n">
         <f aca="false">-前提条件!G21</f>
         <v>-0</v>
       </c>
-      <c r="H11" s="33" t="n">
+      <c r="H11" s="35" t="n">
         <f aca="false">-前提条件!H21</f>
         <v>-0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C12" s="33" t="n">
+        <v>102</v>
+      </c>
+      <c r="C12" s="35" t="n">
         <f aca="false">-前提条件!C22</f>
         <v>-0</v>
       </c>
-      <c r="D12" s="33" t="n">
+      <c r="D12" s="35" t="n">
         <f aca="false">-前提条件!D22</f>
         <v>-15</v>
       </c>
-      <c r="E12" s="33" t="n">
+      <c r="E12" s="35" t="n">
         <f aca="false">-前提条件!E22</f>
         <v>-15</v>
       </c>
-      <c r="F12" s="33" t="n">
+      <c r="F12" s="35" t="n">
         <f aca="false">-前提条件!F22</f>
         <v>-15</v>
       </c>
-      <c r="G12" s="33" t="n">
+      <c r="G12" s="35" t="n">
         <f aca="false">-前提条件!G22</f>
         <v>-15</v>
       </c>
-      <c r="H12" s="33" t="n">
+      <c r="H12" s="35" t="n">
         <f aca="false">-前提条件!H22</f>
         <v>-15</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C13" s="33" t="n">
+        <v>103</v>
+      </c>
+      <c r="C13" s="35" t="n">
         <f aca="false">-前提条件!C23</f>
         <v>-61</v>
       </c>
-      <c r="D13" s="33" t="n">
+      <c r="D13" s="35" t="n">
         <f aca="false">-前提条件!D23</f>
         <v>-61</v>
       </c>
-      <c r="E13" s="33" t="n">
+      <c r="E13" s="35" t="n">
         <f aca="false">-前提条件!E23</f>
         <v>-61</v>
       </c>
-      <c r="F13" s="33" t="n">
+      <c r="F13" s="35" t="n">
         <f aca="false">-前提条件!F23</f>
         <v>-61</v>
       </c>
-      <c r="G13" s="33" t="n">
+      <c r="G13" s="35" t="n">
         <f aca="false">-前提条件!G23</f>
         <v>-61</v>
       </c>
-      <c r="H13" s="33" t="n">
+      <c r="H13" s="35" t="n">
         <f aca="false">-前提条件!H23</f>
         <v>-61</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C14" s="33" t="n">
+        <v>104</v>
+      </c>
+      <c r="C14" s="35" t="n">
         <f aca="false">-前提条件!C24</f>
         <v>-0</v>
       </c>
-      <c r="D14" s="33" t="n">
+      <c r="D14" s="35" t="n">
         <f aca="false">-前提条件!D24</f>
         <v>-0</v>
       </c>
-      <c r="E14" s="33" t="n">
+      <c r="E14" s="35" t="n">
         <f aca="false">-前提条件!E24</f>
         <v>-0</v>
       </c>
-      <c r="F14" s="33" t="n">
+      <c r="F14" s="35" t="n">
         <f aca="false">-前提条件!F24</f>
         <v>-400</v>
       </c>
-      <c r="G14" s="33" t="n">
+      <c r="G14" s="35" t="n">
         <f aca="false">-前提条件!G24</f>
         <v>-400</v>
       </c>
-      <c r="H14" s="33" t="n">
+      <c r="H14" s="35" t="n">
         <f aca="false">-前提条件!H24</f>
         <v>-0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="C15" s="34" t="n">
+      <c r="A15" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="C15" s="36" t="n">
         <f aca="false">SUM(C7,C10:C14)</f>
         <v>577.6</v>
       </c>
-      <c r="D15" s="34" t="n">
+      <c r="D15" s="36" t="n">
         <f aca="false">SUM(D7,D10:D14)</f>
         <v>582.6</v>
       </c>
-      <c r="E15" s="34" t="n">
+      <c r="E15" s="36" t="n">
         <f aca="false">SUM(E7,E10:E14)</f>
         <v>604.6</v>
       </c>
-      <c r="F15" s="34" t="n">
+      <c r="F15" s="36" t="n">
         <f aca="false">SUM(F7,F10:F14)</f>
         <v>249.938001817181</v>
       </c>
-      <c r="G15" s="34" t="n">
+      <c r="G15" s="36" t="n">
         <f aca="false">SUM(G7,G10:G14)</f>
         <v>276.349606203069</v>
       </c>
-      <c r="H15" s="34" t="n">
+      <c r="H15" s="36" t="n">
         <f aca="false">SUM(H7,H10:H14)</f>
         <v>703.880303030303</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C16" s="7" t="n">
         <f aca="false">前提条件!$B$28</f>
@@ -6668,684 +7105,684 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="C17" s="35" t="n">
+        <v>107</v>
+      </c>
+      <c r="C17" s="37" t="n">
         <f aca="false">C15-C16</f>
         <v>577.6</v>
       </c>
-      <c r="D17" s="35" t="n">
+      <c r="D17" s="37" t="n">
         <f aca="false">D15-D16</f>
         <v>582.6</v>
       </c>
-      <c r="E17" s="35" t="n">
+      <c r="E17" s="37" t="n">
         <f aca="false">E15-E16</f>
         <v>604.6</v>
       </c>
-      <c r="F17" s="35" t="n">
+      <c r="F17" s="37" t="n">
         <f aca="false">F15-F16</f>
         <v>249.938001817181</v>
       </c>
-      <c r="G17" s="35" t="n">
+      <c r="G17" s="37" t="n">
         <f aca="false">G15-G16</f>
         <v>276.349606203069</v>
       </c>
-      <c r="H17" s="35" t="n">
+      <c r="H17" s="37" t="n">
         <f aca="false">H15-H16</f>
         <v>703.880303030303</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C18" s="36" t="n">
+        <v>108</v>
+      </c>
+      <c r="C18" s="38" t="n">
         <f aca="false">C35*前提条件!$B$35</f>
         <v>80</v>
       </c>
-      <c r="D18" s="36" t="n">
+      <c r="D18" s="38" t="n">
         <f aca="false">D35*前提条件!$B$35</f>
         <v>69.8712310368397</v>
       </c>
-      <c r="E18" s="36" t="n">
+      <c r="E18" s="38" t="n">
         <f aca="false">E35*前提条件!$B$35</f>
         <v>59.3373113151529</v>
       </c>
-      <c r="F18" s="36" t="n">
+      <c r="F18" s="38" t="n">
         <f aca="false">F35*前提条件!$B$35</f>
         <v>48.3820348045987</v>
       </c>
-      <c r="G18" s="36" t="n">
+      <c r="G18" s="38" t="n">
         <f aca="false">G35*前提条件!$B$35</f>
         <v>36.9885472336223</v>
       </c>
-      <c r="H18" s="36" t="n">
+      <c r="H18" s="38" t="n">
         <f aca="false">H35*前提条件!$B$35</f>
         <v>25.1393201598069</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C19" s="36" t="n">
+        <v>109</v>
+      </c>
+      <c r="C19" s="38" t="n">
         <f aca="false">C17-C18</f>
         <v>497.6</v>
       </c>
-      <c r="D19" s="36" t="n">
+      <c r="D19" s="38" t="n">
         <f aca="false">D17-D18</f>
         <v>512.72876896316</v>
       </c>
-      <c r="E19" s="36" t="n">
+      <c r="E19" s="38" t="n">
         <f aca="false">E17-E18</f>
         <v>545.262688684847</v>
       </c>
-      <c r="F19" s="36" t="n">
+      <c r="F19" s="38" t="n">
         <f aca="false">F17-F18</f>
         <v>201.555967012582</v>
       </c>
-      <c r="G19" s="36" t="n">
+      <c r="G19" s="38" t="n">
         <f aca="false">G17-G18</f>
         <v>239.361058969447</v>
       </c>
-      <c r="H19" s="36" t="n">
+      <c r="H19" s="38" t="n">
         <f aca="false">H17-H18</f>
         <v>678.740982870496</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C20" s="36" t="n">
+        <v>110</v>
+      </c>
+      <c r="C20" s="38" t="n">
         <f aca="false">MAX(0,C19)*前提条件!$B$27</f>
         <v>171.1744</v>
       </c>
-      <c r="D20" s="36" t="n">
+      <c r="D20" s="38" t="n">
         <f aca="false">MAX(0,D19)*前提条件!$B$27</f>
         <v>176.378696523327</v>
       </c>
-      <c r="E20" s="36" t="n">
+      <c r="E20" s="38" t="n">
         <f aca="false">MAX(0,E19)*前提条件!$B$27</f>
         <v>187.570364907587</v>
       </c>
-      <c r="F20" s="36" t="n">
+      <c r="F20" s="38" t="n">
         <f aca="false">MAX(0,F19)*前提条件!$B$27</f>
         <v>69.3352526523282</v>
       </c>
-      <c r="G20" s="36" t="n">
+      <c r="G20" s="38" t="n">
         <f aca="false">MAX(0,G19)*前提条件!$B$27</f>
         <v>82.3402042854898</v>
       </c>
-      <c r="H20" s="36" t="n">
+      <c r="H20" s="38" t="n">
         <f aca="false">MAX(0,H19)*前提条件!$B$27</f>
         <v>233.486898107451</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="26" t="s">
+      <c r="A21" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="34" t="n">
+      <c r="C21" s="36" t="n">
         <f aca="false">C19-C20</f>
         <v>326.4256</v>
       </c>
-      <c r="D21" s="34" t="n">
+      <c r="D21" s="36" t="n">
         <f aca="false">D19-D20</f>
         <v>336.350072439833</v>
       </c>
-      <c r="E21" s="34" t="n">
+      <c r="E21" s="36" t="n">
         <f aca="false">E19-E20</f>
         <v>357.69232377726</v>
       </c>
-      <c r="F21" s="34" t="n">
+      <c r="F21" s="36" t="n">
         <f aca="false">F19-F20</f>
         <v>132.220714360254</v>
       </c>
-      <c r="G21" s="34" t="n">
+      <c r="G21" s="36" t="n">
         <f aca="false">G19-G20</f>
         <v>157.020854683957</v>
       </c>
-      <c r="H21" s="34" t="n">
+      <c r="H21" s="36" t="n">
         <f aca="false">H19-H20</f>
         <v>445.254084763046</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="36" t="n">
+      <c r="C24" s="38" t="n">
         <f aca="false">C21</f>
         <v>326.4256</v>
       </c>
-      <c r="D24" s="36" t="n">
+      <c r="D24" s="38" t="n">
         <f aca="false">D21</f>
         <v>336.350072439833</v>
       </c>
-      <c r="E24" s="36" t="n">
+      <c r="E24" s="38" t="n">
         <f aca="false">E21</f>
         <v>357.69232377726</v>
       </c>
-      <c r="F24" s="36" t="n">
+      <c r="F24" s="38" t="n">
         <f aca="false">F21</f>
         <v>132.220714360254</v>
       </c>
-      <c r="G24" s="36" t="n">
+      <c r="G24" s="38" t="n">
         <f aca="false">G21</f>
         <v>157.020854683957</v>
       </c>
-      <c r="H24" s="36" t="n">
+      <c r="H24" s="38" t="n">
         <f aca="false">H21</f>
         <v>445.254084763046</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C25" s="33" t="n">
+        <v>106</v>
+      </c>
+      <c r="C25" s="35" t="n">
         <f aca="false">C16</f>
         <v>0</v>
       </c>
-      <c r="D25" s="33" t="n">
+      <c r="D25" s="35" t="n">
         <f aca="false">D16</f>
         <v>0</v>
       </c>
-      <c r="E25" s="33" t="n">
+      <c r="E25" s="35" t="n">
         <f aca="false">E16</f>
         <v>0</v>
       </c>
-      <c r="F25" s="33" t="n">
+      <c r="F25" s="35" t="n">
         <f aca="false">F16</f>
         <v>0</v>
       </c>
-      <c r="G25" s="33" t="n">
+      <c r="G25" s="35" t="n">
         <f aca="false">G16</f>
         <v>0</v>
       </c>
-      <c r="H25" s="33" t="n">
+      <c r="H25" s="35" t="n">
         <f aca="false">H16</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C26" s="33" t="n">
+        <v>112</v>
+      </c>
+      <c r="C26" s="35" t="n">
         <f aca="false">-前提条件!$B$29</f>
         <v>-30</v>
       </c>
-      <c r="D26" s="33" t="n">
+      <c r="D26" s="35" t="n">
         <f aca="false">-前提条件!$B$29</f>
         <v>-30</v>
       </c>
-      <c r="E26" s="33" t="n">
+      <c r="E26" s="35" t="n">
         <f aca="false">-前提条件!$B$29</f>
         <v>-30</v>
       </c>
-      <c r="F26" s="33" t="n">
+      <c r="F26" s="35" t="n">
         <f aca="false">-前提条件!$B$29</f>
         <v>-30</v>
       </c>
-      <c r="G26" s="33" t="n">
+      <c r="G26" s="35" t="n">
         <f aca="false">-前提条件!$B$29</f>
         <v>-30</v>
       </c>
-      <c r="H26" s="33" t="n">
+      <c r="H26" s="35" t="n">
         <f aca="false">-前提条件!$B$29</f>
         <v>-30</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="C27" s="36" t="n">
+        <v>113</v>
+      </c>
+      <c r="C27" s="38" t="n">
         <f aca="false">-(前提条件!B31-前提条件!B32*前提条件!B27)</f>
         <v>-36.6</v>
       </c>
-      <c r="D27" s="36" t="n">
+      <c r="D27" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="E27" s="36" t="n">
+      <c r="E27" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="F27" s="36" t="n">
+      <c r="F27" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="G27" s="36" t="n">
+      <c r="G27" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="36" t="n">
+      <c r="H27" s="38" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="C28" s="35" t="n">
+        <v>114</v>
+      </c>
+      <c r="C28" s="37" t="n">
         <f aca="false">SUM(C24:C27)</f>
         <v>259.8256</v>
       </c>
-      <c r="D28" s="35" t="n">
+      <c r="D28" s="37" t="n">
         <f aca="false">SUM(D24:D27)</f>
         <v>306.350072439833</v>
       </c>
-      <c r="E28" s="35" t="n">
+      <c r="E28" s="37" t="n">
         <f aca="false">SUM(E24:E27)</f>
         <v>327.69232377726</v>
       </c>
-      <c r="F28" s="35" t="n">
+      <c r="F28" s="37" t="n">
         <f aca="false">SUM(F24:F27)</f>
         <v>102.220714360254</v>
       </c>
-      <c r="G28" s="35" t="n">
+      <c r="G28" s="37" t="n">
         <f aca="false">SUM(G24:G27)</f>
         <v>127.020854683957</v>
       </c>
-      <c r="H28" s="35" t="n">
+      <c r="H28" s="37" t="n">
         <f aca="false">SUM(H24:H27)</f>
         <v>415.254084763046</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C29" s="36" t="n">
+        <v>115</v>
+      </c>
+      <c r="C29" s="38" t="n">
         <f aca="false">-C38</f>
         <v>-253.219224079008</v>
       </c>
-      <c r="D29" s="36" t="n">
+      <c r="D29" s="38" t="n">
         <f aca="false">-D38</f>
         <v>-263.347993042169</v>
       </c>
-      <c r="E29" s="36" t="n">
+      <c r="E29" s="38" t="n">
         <f aca="false">-E38</f>
         <v>-273.881912763856</v>
       </c>
-      <c r="F29" s="36" t="n">
+      <c r="F29" s="38" t="n">
         <f aca="false">-F38</f>
         <v>-284.83718927441</v>
       </c>
-      <c r="G29" s="36" t="n">
+      <c r="G29" s="38" t="n">
         <f aca="false">-G38</f>
         <v>-296.230676845386</v>
       </c>
-      <c r="H29" s="36" t="n">
+      <c r="H29" s="38" t="n">
         <f aca="false">-H38</f>
         <v>-308.079903919202</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="26" t="s">
-        <v>108</v>
-      </c>
-      <c r="C30" s="34" t="n">
+      <c r="A30" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="C30" s="36" t="n">
         <f aca="false">C28+C29</f>
         <v>6.60637592099158</v>
       </c>
-      <c r="D30" s="34" t="n">
+      <c r="D30" s="36" t="n">
         <f aca="false">D28+D29</f>
         <v>43.0020793976645</v>
       </c>
-      <c r="E30" s="34" t="n">
+      <c r="E30" s="36" t="n">
         <f aca="false">E28+E29</f>
         <v>53.8104110134042</v>
       </c>
-      <c r="F30" s="34" t="n">
+      <c r="F30" s="36" t="n">
         <f aca="false">F28+F29</f>
         <v>-182.616474914156</v>
       </c>
-      <c r="G30" s="34" t="n">
+      <c r="G30" s="36" t="n">
         <f aca="false">G28+G29</f>
         <v>-169.209822161429</v>
       </c>
-      <c r="H30" s="34" t="n">
+      <c r="H30" s="36" t="n">
         <f aca="false">H28+H29</f>
         <v>107.174180843844</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" s="35" t="n">
-        <f aca="false">前提条件!B30+C30</f>
-        <v>106.606375920992</v>
-      </c>
-      <c r="D31" s="35" t="n">
+        <v>117</v>
+      </c>
+      <c r="C31" s="37" t="n">
+        <f aca="false">前提条件!B30+前提条件!B42+C30</f>
+        <v>144.006375920992</v>
+      </c>
+      <c r="D31" s="37" t="n">
         <f aca="false">C31+D30</f>
-        <v>149.608455318656</v>
-      </c>
-      <c r="E31" s="35" t="n">
+        <v>187.008455318656</v>
+      </c>
+      <c r="E31" s="37" t="n">
         <f aca="false">D31+E30</f>
-        <v>203.41886633206</v>
-      </c>
-      <c r="F31" s="35" t="n">
+        <v>240.81886633206</v>
+      </c>
+      <c r="F31" s="37" t="n">
         <f aca="false">E31+F30</f>
-        <v>20.8023914179043</v>
-      </c>
-      <c r="G31" s="35" t="n">
+        <v>58.2023914179043</v>
+      </c>
+      <c r="G31" s="37" t="n">
         <f aca="false">F31+G30</f>
-        <v>-148.407430743525</v>
-      </c>
-      <c r="H31" s="35" t="n">
+        <v>-111.007430743525</v>
+      </c>
+      <c r="H31" s="37" t="n">
         <f aca="false">G31+H30</f>
-        <v>-41.2332498996806</v>
+        <v>-3.83324989968057</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C35" s="32" t="n">
+        <v>119</v>
+      </c>
+      <c r="C35" s="34" t="n">
         <f aca="false">前提条件!B37</f>
         <v>2000</v>
       </c>
-      <c r="D35" s="36" t="n">
+      <c r="D35" s="38" t="n">
         <f aca="false">C39</f>
         <v>1746.78077592099</v>
       </c>
-      <c r="E35" s="36" t="n">
+      <c r="E35" s="38" t="n">
         <f aca="false">D39</f>
         <v>1483.43278287882</v>
       </c>
-      <c r="F35" s="36" t="n">
+      <c r="F35" s="38" t="n">
         <f aca="false">E39</f>
         <v>1209.55087011497</v>
       </c>
-      <c r="G35" s="36" t="n">
+      <c r="G35" s="38" t="n">
         <f aca="false">F39</f>
         <v>924.713680840558</v>
       </c>
-      <c r="H35" s="36" t="n">
+      <c r="H35" s="38" t="n">
         <f aca="false">G39</f>
         <v>628.483003995171</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C36" s="36" t="n">
+        <v>120</v>
+      </c>
+      <c r="C36" s="38" t="n">
         <f aca="false">IF(C35&lt;=0.001,0,-PMT(前提条件!$B$35,前提条件!$B$36,前提条件!$B$37))</f>
         <v>333.219224079008</v>
       </c>
-      <c r="D36" s="36" t="n">
+      <c r="D36" s="38" t="n">
         <f aca="false">IF(D35&lt;=0.001,0,-PMT(前提条件!$B$35,前提条件!$B$36,前提条件!$B$37))</f>
         <v>333.219224079008</v>
       </c>
-      <c r="E36" s="36" t="n">
+      <c r="E36" s="38" t="n">
         <f aca="false">IF(E35&lt;=0.001,0,-PMT(前提条件!$B$35,前提条件!$B$36,前提条件!$B$37))</f>
         <v>333.219224079008</v>
       </c>
-      <c r="F36" s="36" t="n">
+      <c r="F36" s="38" t="n">
         <f aca="false">IF(F35&lt;=0.001,0,-PMT(前提条件!$B$35,前提条件!$B$36,前提条件!$B$37))</f>
         <v>333.219224079008</v>
       </c>
-      <c r="G36" s="36" t="n">
+      <c r="G36" s="38" t="n">
         <f aca="false">IF(G35&lt;=0.001,0,-PMT(前提条件!$B$35,前提条件!$B$36,前提条件!$B$37))</f>
         <v>333.219224079008</v>
       </c>
-      <c r="H36" s="36" t="n">
+      <c r="H36" s="38" t="n">
         <f aca="false">IF(H35&lt;=0.001,0,-PMT(前提条件!$B$35,前提条件!$B$36,前提条件!$B$37))</f>
         <v>333.219224079008</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="C37" s="36" t="n">
+        <v>121</v>
+      </c>
+      <c r="C37" s="38" t="n">
         <f aca="false">C18</f>
         <v>80</v>
       </c>
-      <c r="D37" s="36" t="n">
+      <c r="D37" s="38" t="n">
         <f aca="false">D18</f>
         <v>69.8712310368397</v>
       </c>
-      <c r="E37" s="36" t="n">
+      <c r="E37" s="38" t="n">
         <f aca="false">E18</f>
         <v>59.3373113151529</v>
       </c>
-      <c r="F37" s="36" t="n">
+      <c r="F37" s="38" t="n">
         <f aca="false">F18</f>
         <v>48.3820348045987</v>
       </c>
-      <c r="G37" s="36" t="n">
+      <c r="G37" s="38" t="n">
         <f aca="false">G18</f>
         <v>36.9885472336223</v>
       </c>
-      <c r="H37" s="36" t="n">
+      <c r="H37" s="38" t="n">
         <f aca="false">H18</f>
         <v>25.1393201598069</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C38" s="36" t="n">
+        <v>122</v>
+      </c>
+      <c r="C38" s="38" t="n">
         <f aca="false">MIN(C35,C36-C37)</f>
         <v>253.219224079008</v>
       </c>
-      <c r="D38" s="36" t="n">
+      <c r="D38" s="38" t="n">
         <f aca="false">MIN(D35,D36-D37)</f>
         <v>263.347993042169</v>
       </c>
-      <c r="E38" s="36" t="n">
+      <c r="E38" s="38" t="n">
         <f aca="false">MIN(E35,E36-E37)</f>
         <v>273.881912763856</v>
       </c>
-      <c r="F38" s="36" t="n">
+      <c r="F38" s="38" t="n">
         <f aca="false">MIN(F35,F36-F37)</f>
         <v>284.83718927441</v>
       </c>
-      <c r="G38" s="36" t="n">
+      <c r="G38" s="38" t="n">
         <f aca="false">MIN(G35,G36-G37)</f>
         <v>296.230676845386</v>
       </c>
-      <c r="H38" s="36" t="n">
+      <c r="H38" s="38" t="n">
         <f aca="false">MIN(H35,H36-H37)</f>
         <v>308.079903919202</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="C39" s="35" t="n">
+        <v>123</v>
+      </c>
+      <c r="C39" s="37" t="n">
         <f aca="false">C35-C38</f>
         <v>1746.78077592099</v>
       </c>
-      <c r="D39" s="35" t="n">
+      <c r="D39" s="37" t="n">
         <f aca="false">D35-D38</f>
         <v>1483.43278287882</v>
       </c>
-      <c r="E39" s="35" t="n">
+      <c r="E39" s="37" t="n">
         <f aca="false">E35-E38</f>
         <v>1209.55087011497</v>
       </c>
-      <c r="F39" s="35" t="n">
+      <c r="F39" s="37" t="n">
         <f aca="false">F35-F38</f>
         <v>924.713680840558</v>
       </c>
-      <c r="G39" s="35" t="n">
+      <c r="G39" s="37" t="n">
         <f aca="false">G35-G38</f>
         <v>628.483003995171</v>
       </c>
-      <c r="H39" s="35" t="n">
+      <c r="H39" s="37" t="n">
         <f aca="false">H35-H38</f>
         <v>320.40310007597</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="37" t="s">
-        <v>115</v>
-      </c>
-      <c r="C40" s="38" t="n">
+      <c r="A40" s="39" t="s">
+        <v>124</v>
+      </c>
+      <c r="C40" s="40" t="n">
         <f aca="false">IF(C36=0,0,(C15-C20-前提条件!$B$29)/C36)</f>
         <v>1.12966351518407</v>
       </c>
-      <c r="D40" s="38" t="n">
+      <c r="D40" s="40" t="n">
         <f aca="false">IF(D36=0,0,(D15-D20-前提条件!$B$29)/D36)</f>
         <v>1.12905041573312</v>
       </c>
-      <c r="E40" s="38" t="n">
+      <c r="E40" s="40" t="n">
         <f aca="false">IF(E36=0,0,(E15-E20-前提条件!$B$29)/E36)</f>
         <v>1.16148651435742</v>
       </c>
-      <c r="F40" s="38" t="n">
+      <c r="F40" s="40" t="n">
         <f aca="false">IF(F36=0,0,(F15-F20-前提条件!$B$29)/F36)</f>
         <v>0.451962966965986</v>
       </c>
-      <c r="G40" s="38" t="n">
+      <c r="G40" s="40" t="n">
         <f aca="false">IF(G36=0,0,(G15-G20-前提条件!$B$29)/G36)</f>
         <v>0.492196698347428</v>
       </c>
-      <c r="H40" s="38" t="n">
+      <c r="H40" s="40" t="n">
         <f aca="false">IF(H36=0,0,(H15-H20-前提条件!$B$29)/H36)</f>
         <v>1.32163264631585</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="18" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="11" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="C44" s="36" t="n">
+        <v>127</v>
+      </c>
+      <c r="C44" s="38" t="n">
         <f aca="false">前提条件!B32*前提条件!B27</f>
         <v>77.4</v>
       </c>
-      <c r="D44" s="36" t="n">
+      <c r="D44" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="E44" s="36" t="n">
+      <c r="E44" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="F44" s="36" t="n">
+      <c r="F44" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="G44" s="36" t="n">
+      <c r="G44" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="H44" s="36" t="n">
+      <c r="H44" s="38" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="C45" s="36" t="n">
+        <v>128</v>
+      </c>
+      <c r="C45" s="38" t="n">
         <f aca="false">-C14*前提条件!$B$27</f>
         <v>0</v>
       </c>
-      <c r="D45" s="36" t="n">
+      <c r="D45" s="38" t="n">
         <f aca="false">-D14*前提条件!$B$27</f>
         <v>0</v>
       </c>
-      <c r="E45" s="36" t="n">
+      <c r="E45" s="38" t="n">
         <f aca="false">-E14*前提条件!$B$27</f>
         <v>0</v>
       </c>
-      <c r="F45" s="36" t="n">
+      <c r="F45" s="38" t="n">
         <f aca="false">-F14*前提条件!$B$27</f>
         <v>137.6</v>
       </c>
-      <c r="G45" s="36" t="n">
+      <c r="G45" s="38" t="n">
         <f aca="false">-G14*前提条件!$B$27</f>
         <v>137.6</v>
       </c>
-      <c r="H45" s="36" t="n">
+      <c r="H45" s="38" t="n">
         <f aca="false">-H14*前提条件!$B$27</f>
         <v>0</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="C46" s="35" t="n">
+        <v>129</v>
+      </c>
+      <c r="C46" s="37" t="n">
         <f aca="false">C44+C45</f>
         <v>77.4</v>
       </c>
-      <c r="D46" s="35" t="n">
+      <c r="D46" s="37" t="n">
         <f aca="false">D44+D45</f>
         <v>0</v>
       </c>
-      <c r="E46" s="35" t="n">
+      <c r="E46" s="37" t="n">
         <f aca="false">E44+E45</f>
         <v>0</v>
       </c>
-      <c r="F46" s="35" t="n">
+      <c r="F46" s="37" t="n">
         <f aca="false">F44+F45</f>
         <v>137.6</v>
       </c>
-      <c r="G46" s="35" t="n">
+      <c r="G46" s="37" t="n">
         <f aca="false">G44+G45</f>
         <v>137.6</v>
       </c>
-      <c r="H46" s="35" t="n">
+      <c r="H46" s="37" t="n">
         <f aca="false">H44+H45</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="26" t="s">
-        <v>121</v>
-      </c>
-      <c r="C47" s="34" t="n">
+      <c r="A47" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="C47" s="36" t="n">
         <f aca="false">C46</f>
         <v>77.4</v>
       </c>
-      <c r="D47" s="34" t="n">
+      <c r="D47" s="36" t="n">
         <f aca="false">C47+D46</f>
         <v>77.4</v>
       </c>
-      <c r="E47" s="34" t="n">
+      <c r="E47" s="36" t="n">
         <f aca="false">D47+E46</f>
         <v>77.4</v>
       </c>
-      <c r="F47" s="34" t="n">
+      <c r="F47" s="36" t="n">
         <f aca="false">E47+F46</f>
         <v>215</v>
       </c>
-      <c r="G47" s="34" t="n">
+      <c r="G47" s="36" t="n">
         <f aca="false">F47+G46</f>
         <v>352.6</v>
       </c>
-      <c r="H47" s="34" t="n">
+      <c r="H47" s="36" t="n">
         <f aca="false">G47+H46</f>
         <v>352.6</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
